--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_704_Viet_Nam.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_704_Viet_Nam.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R754f6b501c824420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re2c02f9bedde49a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R400eff422d474ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb5c632929b4c4f9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R916ebeb0faa74254"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R935a3eb5b1ad4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re0c9ee3e75614ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R701ab1fd90374b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3de1242926474fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R03a6897fab9346f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8063990257b948ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ref0ee36a4b3f4da1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ704CommercialTable" displayName="EEZ704CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ704CommercialTable" displayName="EEZ704CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ704FunctionalTable" displayName="EEZ704FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ704FunctionalTable" displayName="EEZ704FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ704ValidationTable" displayName="EEZ704ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ704ValidationTable" displayName="EEZ704ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5317,7 +5271,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5387223743fb476d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82bf98ccb7434584"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5327,20 +5281,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5348,552 +5292,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>99030.6233078043</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1838967333272</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>152.7202876300815</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>99030.6233078043</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>153.00054957566218</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$70,A2,'Species'!$U$2:$U$70))</x:f>
-        <x:v>15151739.790914439</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1838967333272</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>152.7202876300815</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>15123985.275754124</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>27754.51516031474</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0018351323843728</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0018351323843728631</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>246594.81539961678</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.032157947735313</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>107.68567824191003</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>246594.81539961678</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>177.3204477772812</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$70,A3,'Species'!$U$2:$U$70))</x:f>
-        <x:v>43726303.08621605</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.032157947735313</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>107.68567824191003</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>26554729.94724633</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>17171573.138969716</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.6466483814025896</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.6466483814025896</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5004.8238130052005</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5004.8238130052005</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$70,A4,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>12285385.635216605</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>12285385.635216605</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>119122.6628343685</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1661149941850844</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>146.59359458032256</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>119122.6628343685</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>154.5182622325222</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$70,A5,'Species'!$U$2:$U$70))</x:f>
-        <x:v>18406626.85367728</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1661149941850844</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>146.59359458032256</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>17462619.340869874</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>944007.5128074065</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.054058757989303</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.054058757989303007</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>30984</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>30984</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$70,A6,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>390065.44959030487</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>390065.44959030487</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1545286.7625302393</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9746287886894005</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>943.2542891398608</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1545286.7625302393</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1289.1927081463575</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$70,A7,'Species'!$U$2:$U$70))</x:f>
-        <x:v>1992172426.2490766</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9746287886894005</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>943.2542891398608</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1457598366.7076979</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>534574059.54137874</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3667499029577195</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3667499029577196</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2726784.1113102366</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6405539563431186</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>437.0729772383654</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2726784.1113102366</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>629.2339402297579</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$70,A8,'Species'!$U$2:$U$70))</x:f>
-        <x:v>1715785110.5156388</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6405539563431186</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>437.0729772383654</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1191803649.8166356</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>523981460.6990032</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4396541836229653</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4396541836229652</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>25117.713352990606</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.000085570943292</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1000.1970537909659</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>25117.713352990606</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1000.3005098988945</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$70,A9,'Species'!$U$2:$U$70))</x:f>
-        <x:v>25125261.474490773</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.000085570943292</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1000.1970537909659</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>25122662.893627208</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2598.5808635652065</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0001034357255267</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00010343572552670684</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>350379.6244418383</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.210315366131071</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1622.9882143824627</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>350379.6244418383</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1634.8302548664685</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$70,A10,'Species'!$U$2:$U$70))</x:f>
-        <x:v>572811210.726268</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.210315366131071</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1622.9882143824627</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>568662001.028857</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4149209.6974110603</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0072964426845896</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.007296442684589553</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03d2fb740482456d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81478782996c4ad1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5903,20 +5488,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5924,984 +5499,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>465278.3500621186</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7351133162290164</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>543.3920950037051</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>465278.3500621186</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>578.6403708601555</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$70,A2,'Species'!$U$2:$U$70))</x:f>
-        <x:v>269228837.03314555</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7351133162290164</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>543.3920950037051</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>252828577.4001219</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>16400259.63302365</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.064867111944663</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.06486711194466319</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>16606.949519653597</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>16606.949519653597</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$70,A3,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4789496.558551422</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4789496.558551422</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>48753.82975575601</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.340130119792569</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2188.4172015593176</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>48753.82975575601</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2538.611554102582</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$70,A4,'Species'!$U$2:$U$70))</x:f>
-        <x:v>123767035.52471246</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.340130119792569</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2188.4172015593176</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>106693719.67939095</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>17073315.845321506</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.160021751014267</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.16002175101426708</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>25647.4950050216</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.38</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2398.83291901949</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>25647.4950050216</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2398.83291901949</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$70,A5,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>61524055.30843375</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.38</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2398.83291901949</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>61524055.30843375</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>373611.51117895194</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.219434611744907</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1657.427772386095</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>373611.51117895194</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1675.0497275158398</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$70,A6,'Species'!$U$2:$U$70))</x:f>
-        <x:v>625817859.9970846</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.219434611744907</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1657.427772386095</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>619234094.711133</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>6583765.285951614</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0106321104444724</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.010632110444472345</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>25117.713352990606</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.000085570943292</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1000.1970537909659</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>25117.713352990606</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1000.3005098988945</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$70,A7,'Species'!$U$2:$U$70))</x:f>
-        <x:v>25125261.474490773</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.000085570943292</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1000.1970537909659</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>25122662.893627208</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2598.5808635652065</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0001034357255267</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00010343572552670684</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>116322.1646667821</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>2.877041919643876</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>75.34282837944933</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>116322.1646667821</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>183.80580018994428</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$70,A8,'Species'!$U$2:$U$70))</x:f>
-        <x:v>21380688.55640435</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>2.877041919643876</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>75.34282837944933</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>8764040.889215408</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>12616647.66718894</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.4395925152191333</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.4395925152191336</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>368114.76064278814</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.319607994188393</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>208.74111271577186</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>368114.76064278814</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>210.03916388204922</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$70,A9,'Species'!$U$2:$U$70))</x:f>
-        <x:v>77318516.5380519</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.319607994188393</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>208.74111271577186</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>76840684.74367562</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>477831.7943762839</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0062184739239406</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.006218473923940558</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1707547.1148410395</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8976187878316497</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>789.9848958022493</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1707547.1148410395</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1134.9337203945038</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$70,A10,'Species'!$U$2:$U$70))</x:f>
-        <x:v>1937952799.7954419</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8976187878316497</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>789.9848958022493</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1348936429.59513</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>589016370.2003119</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.4366524302239354</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.4366524302239353</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>629320.5060519546</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.0726640972301125</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1182.1268922578313</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>629320.5060519546</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1336.539868385387</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$70,A11,'Species'!$U$2:$U$70))</x:f>
-        <x:v>841111946.3309046</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.0726640972301125</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1182.1268922578313</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>743936694.0533228</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>97175252.27758181</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.130623012756804</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.13062301275680405</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>405502.7673606192</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5773270943560282</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>377.8566712904995</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>405502.7673606192</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>458.6024814258897</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$70,A12,'Species'!$U$2:$U$70))</x:f>
-        <x:v>185964575.33664525</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5773270943560282</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>377.8566712904995</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>153221925.87396938</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>32742649.46267587</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2136942821721735</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.21369428217217354</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>32467.381899785003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.115087304267102</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>13.03428774543779</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>32467.381899785003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>13.244480138669465</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$70,A13,'Species'!$U$2:$U$70))</x:f>
-        <x:v>430013.59472629894</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.115087304267102</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>13.03428774543779</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>423189.1980228164</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>6824.396703482547</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.016126112706484</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.01612611270648408</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>130272.65073283469</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.170663091068223</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>148.13684506948732</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>130272.65073283469</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>171.52959123890435</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$70,A14,'Species'!$U$2:$U$70))</x:f>
-        <x:v>22345614.529811688</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.170663091068223</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>148.13684506948732</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>19298179.478401367</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>3047435.051410321</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1579130847456895</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.15791308474568952</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>435672.2818216477</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2399999999999998</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>173.78008287493745</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>435672.2818216477</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>173.78008287493765</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$70,A15,'Species'!$U$2:$U$70))</x:f>
-        <x:v>75711165.24127913</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2399999999999998</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>173.78008287493745</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>75711165.24127905</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>7.450580596923828e-8</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>9.840795044139198e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>151959.327846235</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>524.8074602497728</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>151959.327846235</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$70,A16,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>79749388.90824518</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>79749388.90824518</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>211105.508438916</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1712100741184486</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>148.3235372674348</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>211105.508438916</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>148.51099646703494</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$70,A17,'Species'!$U$2:$U$70))</x:f>
-        <x:v>31351489.41794347</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1712100741184486</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>148.3235372674348</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>31311915.74830033</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>39573.66964314133</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0012638533509497</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.001263853350949613</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>5004.8238130052005</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>5004.8238130052005</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$70,A18,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>12285385.635216605</x:v>
       </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>12285385.635216605</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra453e1395da84891"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd62ad75a07bd4d65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7076,7 +6012,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7175,7 +6111,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4395854129.781089</x:v>
+        <x:v>3315003466.095495</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7189,7 +6125,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4395854129.781089</x:v>
+        <x:v>3620671605.916037</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7203,7 +6139,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>9.5367431640625e-7</x:v>
+        <x:v>-1080850663.6855927</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7217,7 +6153,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>9.5367431640625e-7</x:v>
+        <x:v>-775182523.8650508</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7228,9 +6164,9 @@
         <x:v>EEZ_704</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7242,47 +6178,19 @@
         <x:v>EEZ_704</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_704</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_704</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cab5cc95f2f426c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R826fb16e1c30492f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7329,7 +6237,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
